--- a/figures/supporting_information/S7_Table.xlsx
+++ b/figures/supporting_information/S7_Table.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P80"/>
+  <dimension ref="A1:P77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,114 +565,114 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>KRAS</t>
+          <t>SOX10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KRAS (3845)</t>
+          <t>SOX10 (6663)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>pancreas</t>
+          <t>skin</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-1.888434536504414</v>
+        <v>-1.665313946694566</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.383151857934958</v>
+        <v>-1.374373056890616</v>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="G2" t="n">
-        <v>1.991472929701745e-12</v>
+        <v>1.453359713299149e-27</v>
       </c>
       <c r="H2" t="n">
-        <v>5.03582747120326e-09</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-1.257313450971388</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-0.9075659555254312</v>
-      </c>
-      <c r="K2" t="n">
-        <v>23</v>
-      </c>
-      <c r="L2" t="n">
-        <v>6.378901939418363e-11</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.687335837631147e-06</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
+        <v>4.646380622276572e-23</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>meets rule</t>
+          <t>not testable</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SOX10</t>
+          <t>KRAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SOX10 (6663)</t>
+          <t>KRAS (3845)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>skin</t>
+          <t>pancreas</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-1.670209320059542</v>
+        <v>-1.86019184995362</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.378311916898018</v>
+        <v>-1.355846247765565</v>
       </c>
       <c r="F3" t="n">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="G3" t="n">
-        <v>7.233291820809494e-29</v>
+        <v>2.620932685231117e-11</v>
       </c>
       <c r="H3" t="n">
-        <v>3.237469519866092e-24</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+        <v>5.381075368454397e-08</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-1.257313450971388</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-0.9075659555254312</v>
+      </c>
+      <c r="K3" t="n">
+        <v>23</v>
+      </c>
+      <c r="L3" t="n">
+        <v>6.378901939418363e-11</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.687335837631147e-06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>not testable</t>
+          <t>meets rule</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CFLAR</t>
+          <t>HNF1B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CFLAR (8837)</t>
+          <t>HNF1B (6928)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -681,19 +681,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.715027919050082</v>
+        <v>-1.309117850188102</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.152487627196181</v>
+        <v>-1.153061180935798</v>
       </c>
       <c r="F4" t="n">
         <v>31</v>
       </c>
       <c r="G4" t="n">
-        <v>8.494597795465052e-09</v>
+        <v>3.353224719957459e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>8.720191712606542e-06</v>
+        <v>3.858182434277223e-06</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
@@ -711,12 +711,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HNF1B</t>
+          <t>CFLAR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HNF1B (6928)</t>
+          <t>CFLAR (8837)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-1.309117850188102</v>
+        <v>-1.715027919050082</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.151555296152607</v>
+        <v>-1.14941003313538</v>
       </c>
       <c r="F5" t="n">
         <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>3.733996228335591e-09</v>
+        <v>9.518571749556152e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>4.167726428633955e-06</v>
+        <v>9.793822586424351e-06</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
@@ -772,16 +772,16 @@
         <v>-1.55427191249818</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.123606136150321</v>
+        <v>-1.122754221813722</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>1.502694117736052e-05</v>
+        <v>1.479021252060292e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0047464666938756</v>
+        <v>0.0048004267801007</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
@@ -816,16 +816,16 @@
         <v>-1.356473385502453</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.057744111463523</v>
+        <v>-1.056202281613122</v>
       </c>
       <c r="F7" t="n">
         <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>1.19433321148498e-23</v>
+        <v>1.300041428431011e-23</v>
       </c>
       <c r="H7" t="n">
-        <v>2.055994094089369e-19</v>
+        <v>2.094094291521859e-19</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-1.097895688783254</v>
+        <v>-1.108464193096825</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.027559895688165</v>
+        <v>-1.037382726441304</v>
       </c>
       <c r="F8" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G8" t="n">
-        <v>1.007761381640084e-22</v>
+        <v>2.523461354070141e-21</v>
       </c>
       <c r="H8" t="n">
-        <v>1.326625974803198e-18</v>
+        <v>2.823620773483398e-17</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
@@ -904,16 +904,16 @@
         <v>-1.181373370396734</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.027249340913516</v>
+        <v>-1.028137366834277</v>
       </c>
       <c r="F9" t="n">
         <v>41</v>
       </c>
       <c r="G9" t="n">
-        <v>9.114557782826668e-19</v>
+        <v>1.216704443691734e-18</v>
       </c>
       <c r="H9" t="n">
-        <v>6.350751401432671e-15</v>
+        <v>8.378020895432347e-15</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
@@ -948,16 +948,16 @@
         <v>-1.101619065138771</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9790511831748312</v>
+        <v>-0.979158079276144</v>
       </c>
       <c r="F10" t="n">
         <v>18</v>
       </c>
       <c r="G10" t="n">
-        <v>7.363813788970447e-10</v>
+        <v>7.278402476850272e-10</v>
       </c>
       <c r="H10" t="n">
-        <v>1.01411951133957e-06</v>
+        <v>1.014847383858619e-06</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -992,16 +992,16 @@
         <v>-1.174440146267304</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9377736274129606</v>
+        <v>-0.9375967736472</v>
       </c>
       <c r="F11" t="n">
         <v>84</v>
       </c>
       <c r="G11" t="n">
-        <v>1.673417583547037e-34</v>
+        <v>1.774537286215361e-34</v>
       </c>
       <c r="H11" t="n">
-        <v>1.872466421565998e-29</v>
+        <v>1.985614060067463e-29</v>
       </c>
       <c r="I11" t="n">
         <v>-0.6626589733929366</v>
@@ -1033,91 +1033,77 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CTNNB1</t>
+          <t>SKP2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CTNNB1 (1499)</t>
+          <t>SKP2 (6502)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>bowel</t>
+          <t>cervix</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1.050836261465989</v>
+        <v>-1.569685120222577</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9155821860809426</v>
+        <v>-0.9040173394232291</v>
       </c>
       <c r="F12" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="G12" t="n">
-        <v>3.206434391655334e-11</v>
+        <v>1.596977522470725e-06</v>
       </c>
       <c r="H12" t="n">
-        <v>6.340801206176097e-08</v>
-      </c>
-      <c r="I12" t="n">
-        <v>-0.938690476488468</v>
-      </c>
-      <c r="J12" t="n">
-        <v>-0.7986913477094655</v>
-      </c>
-      <c r="K12" t="n">
-        <v>30</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.407631991611357e-15</v>
-      </c>
-      <c r="M12" t="n">
-        <v>2.948932717146128e-10</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
+        <v>0.0007889333361257</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>significant, below rule</t>
+          <t>not testable</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SKP2</t>
+          <t>MDM2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SKP2 (6502)</t>
+          <t>MDM2 (4193)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>cervix</t>
+          <t>kidney</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-1.569685120222577</v>
+        <v>-1.290220009827672</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.906106271680397</v>
+        <v>-0.8636085924861948</v>
       </c>
       <c r="F13" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G13" t="n">
-        <v>1.536299452558176e-06</v>
+        <v>2.75418053604021e-08</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0007523144121187</v>
+        <v>2.480308591831672e-05</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
@@ -1145,23 +1131,23 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>kidney</t>
+          <t>pleura</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-1.290220009827672</v>
+        <v>-1.274670024950142</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.8639512744068607</v>
+        <v>-0.8431523342656835</v>
       </c>
       <c r="F14" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>2.91658607550313e-08</v>
+        <v>0.0002343114589877</v>
       </c>
       <c r="H14" t="n">
-        <v>2.595233954448539e-05</v>
+        <v>0.0347893031573204</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
@@ -1179,33 +1165,33 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MDM2</t>
+          <t>FERMT2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MDM2 (4193)</t>
+          <t>FERMT2 (10979)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>pleura</t>
+          <t>kidney</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-1.274670024950142</v>
+        <v>-1.37473381333783</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.8440042486022828</v>
+        <v>-0.8413289126046094</v>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0002385466071611</v>
+        <v>8.758397246066763e-08</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0340569224518542</v>
+        <v>6.865279651483914e-05</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
@@ -1223,33 +1209,33 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FERMT2</t>
+          <t>UMPS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FERMT2 (10979)</t>
+          <t>UMPS (7372)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>kidney</t>
+          <t>myeloid</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-1.37473381333783</v>
+        <v>-1.265894857139244</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8376090773763644</v>
+        <v>-0.8337962085417162</v>
       </c>
       <c r="F16" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G16" t="n">
-        <v>8.317385236426716e-08</v>
+        <v>1.520899494677369e-10</v>
       </c>
       <c r="H16" t="n">
-        <v>6.519591885699882e-05</v>
+        <v>2.50265689311839e-07</v>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
@@ -1267,33 +1253,33 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UMPS</t>
+          <t>NHLRC2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UMPS (7372)</t>
+          <t>NHLRC2 (374354)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>myeloid</t>
+          <t>thyroid</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-1.265894857139244</v>
+        <v>-1.612606018434213</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8332535551178025</v>
+        <v>-0.8078855064342754</v>
       </c>
       <c r="F17" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="G17" t="n">
-        <v>2.037378579686208e-10</v>
+        <v>0.0003053500976732</v>
       </c>
       <c r="H17" t="n">
-        <v>3.303941548251352e-07</v>
+        <v>0.0411459528511413</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
@@ -1311,77 +1297,91 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MDM2</t>
+          <t>ATP1B3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MDM2 (4193)</t>
+          <t>ATP1B3 (483)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>skin</t>
+          <t>lymphoid</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-1.252661993566242</v>
+        <v>-1.074183970826458</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8293536033669171</v>
+        <v>-0.7794726121501208</v>
       </c>
       <c r="F18" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G18" t="n">
-        <v>2.094828789283722e-09</v>
+        <v>6.228441930398051e-35</v>
       </c>
       <c r="H18" t="n">
-        <v>2.540925134630946e-06</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+        <v>1.295925381186712e-29</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.8498783485660965</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.7683691542881097</v>
+      </c>
+      <c r="K18" t="n">
+        <v>10</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5.395572520698441e-07</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.0002359813905628</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>not testable</t>
+          <t>significant, below rule</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NHLRC2</t>
+          <t>MDM2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NHLRC2 (374354)</t>
+          <t>MDM2 (4193)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>thyroid</t>
+          <t>skin</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-1.612606018434213</v>
+        <v>-1.200210115640962</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8059917114552559</v>
+        <v>-0.7756647224429027</v>
       </c>
       <c r="F19" t="n">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0003151559039775</v>
+        <v>2.016306218115502e-08</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0406972598126226</v>
+        <v>1.896043740737577e-05</v>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
@@ -1399,12 +1399,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ATP1B3</t>
+          <t>UMPS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ATP1B3 (483)</t>
+          <t>UMPS (7372)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1413,34 +1413,34 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-1.074183970826458</v>
+        <v>-1.187649371045798</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7794726121501208</v>
+        <v>-0.775405600373415</v>
       </c>
       <c r="F20" t="n">
         <v>84</v>
       </c>
       <c r="G20" t="n">
-        <v>3.7292612481963e-35</v>
+        <v>2.994839411182986e-25</v>
       </c>
       <c r="H20" t="n">
-        <v>8.345695101032257e-30</v>
+        <v>6.382986803894618e-21</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8498783485660965</v>
+        <v>-0.7103105151578404</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7683691542881097</v>
+        <v>-0.4515675055507923</v>
       </c>
       <c r="K20" t="n">
         <v>10</v>
       </c>
       <c r="L20" t="n">
-        <v>5.395572520698441e-07</v>
+        <v>3.228534367996321e-06</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0002359813905628</v>
+        <v>0.0006392864234005</v>
       </c>
       <c r="N20" t="n">
         <v>1</v>
@@ -1457,56 +1457,70 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SEPHS2</t>
+          <t>SDHB</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SEPHS2 (22928)</t>
+          <t>SDHB (6390)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>kidney</t>
+          <t>lymphoid</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1.524245141524018</v>
+        <v>-1.143610907398437</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.776882126008951</v>
+        <v>-0.7745258960462706</v>
       </c>
       <c r="F21" t="n">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="G21" t="n">
-        <v>5.791058857113161e-05</v>
+        <v>3.439702542253339e-26</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0129581020390396</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+        <v>8.47056953597791e-22</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0.8869137877383075</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-0.5952616989895489</v>
+      </c>
+      <c r="K21" t="n">
+        <v>10</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.273148697441189e-06</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.000522195081717</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>not testable</t>
+          <t>significant, below rule</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UMPS</t>
+          <t>NAMPT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UMPS (7372)</t>
+          <t>NAMPT (10135)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1515,218 +1529,204 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-1.187649371045798</v>
+        <v>-1.057275251564049</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.772127397666838</v>
+        <v>-0.770999423393094</v>
       </c>
       <c r="F22" t="n">
         <v>84</v>
       </c>
       <c r="G22" t="n">
-        <v>7.623812205414988e-25</v>
+        <v>1.734571388615196e-29</v>
       </c>
       <c r="H22" t="n">
-        <v>1.624884877660683e-20</v>
+        <v>9.704471594312507e-25</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7103105151578404</v>
+        <v>-1.233514118804231</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4515675055507923</v>
+        <v>-0.8320289078006696</v>
       </c>
       <c r="K22" t="n">
         <v>10</v>
       </c>
       <c r="L22" t="n">
-        <v>3.228534367996321e-06</v>
+        <v>2.922143162187989e-06</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0006392864234005</v>
+        <v>0.000603029600905</v>
       </c>
       <c r="N22" t="n">
         <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>significant, below rule</t>
+          <t>meets rule</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NAMPT</t>
+          <t>SEPHS2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NAMPT (10135)</t>
+          <t>SEPHS2 (22928)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>lymphoid</t>
+          <t>kidney</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-1.057275251564049</v>
+        <v>-1.524245141524018</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7708568973920226</v>
+        <v>-0.7640439407303127</v>
       </c>
       <c r="F23" t="n">
-        <v>84</v>
+        <v>31</v>
       </c>
       <c r="G23" t="n">
-        <v>1.492427678586027e-29</v>
+        <v>6.605439348531504e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>8.349741099423193e-25</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-1.233514118804231</v>
-      </c>
-      <c r="J23" t="n">
-        <v>-0.8320289078006696</v>
-      </c>
-      <c r="K23" t="n">
-        <v>10</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2.922143162187989e-06</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.000603029600905</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1</v>
-      </c>
+        <v>0.0146069957419781</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>meets rule</t>
+          <t>not testable</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SDHB</t>
+          <t>CCND1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SDHB (6390)</t>
+          <t>CCND1 (595)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>lymphoid</t>
+          <t>peripheral nervous system</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-1.143610907398437</v>
+        <v>-1.781991279327073</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.7703567180857969</v>
+        <v>-0.7620790366408952</v>
       </c>
       <c r="F24" t="n">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="G24" t="n">
-        <v>5.481467439571058e-26</v>
+        <v>0.0002425365705829</v>
       </c>
       <c r="H24" t="n">
-        <v>1.291257744808302e-21</v>
+        <v>0.0355449494842596</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8869137877383075</v>
+        <v>-1.382830406763131</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5952616989895489</v>
+        <v>-0.6187715502525587</v>
       </c>
       <c r="K24" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="L24" t="n">
-        <v>2.273148697441189e-06</v>
+        <v>0.0001697341517644</v>
       </c>
       <c r="M24" t="n">
-        <v>0.000522195081717</v>
+        <v>0.0074065040320842</v>
       </c>
       <c r="N24" t="n">
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>significant, below rule</t>
+          <t>meets rule</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CCND1</t>
+          <t>CRKL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CCND1 (595)</t>
+          <t>CRKL (1399)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>peripheral nervous system</t>
+          <t>pancreas</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-1.781991279327073</v>
+        <v>-1.555377014321401</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.7615347765487575</v>
+        <v>-0.7608267092650901</v>
       </c>
       <c r="F25" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="G25" t="n">
-        <v>7.801891422359864e-05</v>
+        <v>3.282639267074094e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.015930487048031</v>
+        <v>0.008688589003653199</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.382830406763131</v>
+        <v>-0.8425327301947045</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6187715502525587</v>
+        <v>-0.1914368888415086</v>
       </c>
       <c r="K25" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0001697341517644</v>
+        <v>0.008611042947851401</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0074065040320842</v>
+        <v>0.0922326833377513</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>meets rule</t>
+          <t>not significant</t>
         </is>
       </c>
     </row>
@@ -1747,19 +1747,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-1.751117706291526</v>
+        <v>-1.760862167813841</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.747392356212476</v>
+        <v>-0.7595372716705364</v>
       </c>
       <c r="F26" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G26" t="n">
-        <v>1.061224440366088e-08</v>
+        <v>7.102873356980818e-09</v>
       </c>
       <c r="H26" t="n">
-        <v>1.067374772572165e-05</v>
+        <v>7.587343566215078e-06</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
@@ -1777,12 +1777,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NAMPT</t>
+          <t>ADSL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NAMPT (10135)</t>
+          <t>ADSL (158)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1791,19 +1791,19 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-1.04487301021957</v>
+        <v>-1.694782825699614</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.7452549194630895</v>
+        <v>-0.7458711036091752</v>
       </c>
       <c r="F27" t="n">
         <v>41</v>
       </c>
       <c r="G27" t="n">
-        <v>3.849105955691162e-14</v>
+        <v>4.323499722485394e-11</v>
       </c>
       <c r="H27" t="n">
-        <v>1.335487592668445e-10</v>
+        <v>8.340981389182286e-08</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
@@ -1821,12 +1821,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ADSL</t>
+          <t>NAMPT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ADSL (158)</t>
+          <t>NAMPT (10135)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1835,19 +1835,19 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-1.694782825699614</v>
+        <v>-1.04487301021957</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.7447748873917154</v>
+        <v>-0.7451313727037595</v>
       </c>
       <c r="F28" t="n">
         <v>41</v>
       </c>
       <c r="G28" t="n">
-        <v>4.621849760333931e-11</v>
+        <v>4.245297501348346e-14</v>
       </c>
       <c r="H28" t="n">
-        <v>8.765435991019069e-08</v>
+        <v>1.4729503956248e-10</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
@@ -1882,16 +1882,16 @@
         <v>-1.575504219990485</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.733054603100721</v>
+        <v>-0.7378181744280528</v>
       </c>
       <c r="F29" t="n">
         <v>84</v>
       </c>
       <c r="G29" t="n">
-        <v>1.215670064353837e-22</v>
+        <v>1.389930687590472e-22</v>
       </c>
       <c r="H29" t="n">
-        <v>1.511412199259516e-18</v>
+        <v>1.77743939206016e-18</v>
       </c>
       <c r="I29" t="n">
         <v>-1.101488672658674</v>
@@ -1923,164 +1923,150 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KIF18A</t>
+          <t>CDAN1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>KIF18A (81930)</t>
+          <t>CDAN1 (146059)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>head and neck</t>
+          <t>lymphoid</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-1.982859442543185</v>
+        <v>-1.655886854258267</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.7265493152316966</v>
+        <v>-0.7206873358025989</v>
       </c>
       <c r="F30" t="n">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0002440711354955</v>
+        <v>1.018664085249719e-13</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0345590366194126</v>
+        <v>3.188340228055831e-10</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.8160878040287975</v>
+        <v>-0.977019416173902</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1818524073044841</v>
+        <v>-0.539108158156004</v>
       </c>
       <c r="K30" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8114412086085991</v>
+        <v>1.306313091393469e-05</v>
       </c>
       <c r="M30" t="n">
-        <v>0.9999999999999653</v>
+        <v>0.001522912450721</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>not significant</t>
+          <t>significant, below rule</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCL2L1</t>
+          <t>FERMT2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BCL2L1 (598)</t>
+          <t>FERMT2 (10979)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>bowel</t>
+          <t>skin</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-1.673854449943091</v>
+        <v>-1.209017506087039</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.7161270544452555</v>
+        <v>-0.7114391449734631</v>
       </c>
       <c r="F31" t="n">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="G31" t="n">
-        <v>4.741196682491173e-07</v>
+        <v>7.115953637156339e-13</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0002883233790696</v>
-      </c>
-      <c r="I31" t="n">
-        <v>-1.223685267646057</v>
-      </c>
-      <c r="J31" t="n">
-        <v>-0.4931080971911801</v>
-      </c>
-      <c r="K31" t="n">
-        <v>30</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.385603955708632e-05</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.0015716712814533</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
+        <v>1.895804412479045e-09</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>significant, below rule</t>
+          <t>not testable</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CDAN1</t>
+          <t>BCL2L1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CDAN1 (146059)</t>
+          <t>BCL2L1 (598)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>lymphoid</t>
+          <t>bowel</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-1.655886854258267</v>
+        <v>-1.673854449943091</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.7110288840300132</v>
+        <v>-0.7076766514895794</v>
       </c>
       <c r="F32" t="n">
-        <v>84</v>
+        <v>31</v>
       </c>
       <c r="G32" t="n">
-        <v>1.712041977588001e-13</v>
+        <v>1.454685425504056e-06</v>
       </c>
       <c r="H32" t="n">
-        <v>5.074662491965958e-10</v>
+        <v>0.0007332056847541</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.977019416173902</v>
+        <v>-1.223685267646057</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.539108158156004</v>
+        <v>-0.4931080971911801</v>
       </c>
       <c r="K32" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="L32" t="n">
-        <v>1.306313091393469e-05</v>
+        <v>1.385603955708632e-05</v>
       </c>
       <c r="M32" t="n">
-        <v>0.001522912450721</v>
+        <v>0.0015716712814533</v>
       </c>
       <c r="N32" t="n">
         <v>1</v>
@@ -2097,33 +2083,33 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FERMT2</t>
+          <t>SOX10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FERMT2 (10979)</t>
+          <t>SOX10 (6663)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>skin</t>
+          <t>eye</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-1.206637670818067</v>
+        <v>-1.011961766589184</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7068852699518278</v>
+        <v>-0.7055650581889913</v>
       </c>
       <c r="F33" t="n">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="G33" t="n">
-        <v>4.791245049457405e-13</v>
+        <v>9.275572433849114e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>1.331963147820556e-09</v>
+        <v>0.0185171785654315</v>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
@@ -2141,44 +2127,58 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SOX10</t>
+          <t>ATP1A1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SOX10 (6663)</t>
+          <t>ATP1A1 (476)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>eye</t>
+          <t>breast</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-1.011961766589184</v>
+        <v>-1.921526807640351</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7055650581889913</v>
+        <v>-0.7008026482652601</v>
       </c>
       <c r="F34" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="G34" t="n">
-        <v>9.186782429602752e-05</v>
+        <v>2.556899586340708e-07</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0178774386654746</v>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+        <v>0.0001733961454476</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-1.126752705383011</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-0.2714354460894485</v>
+      </c>
+      <c r="K34" t="n">
+        <v>25</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.0477090274213294</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.266934402927176</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>not testable</t>
+          <t>not significant</t>
         </is>
       </c>
     </row>
@@ -2202,16 +2202,16 @@
         <v>-1.403718227685325</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7045009613477999</v>
+        <v>-0.6999576551205116</v>
       </c>
       <c r="F35" t="n">
         <v>84</v>
       </c>
       <c r="G35" t="n">
-        <v>2.439690143074347e-16</v>
+        <v>3.79811416484811e-16</v>
       </c>
       <c r="H35" t="n">
-        <v>1.174144166179649e-12</v>
+        <v>1.770787645613075e-12</v>
       </c>
       <c r="I35" t="n">
         <v>-0.8179399655932764</v>
@@ -2260,16 +2260,16 @@
         <v>-1.192344899201941</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6876945661074978</v>
+        <v>-0.6885124293263206</v>
       </c>
       <c r="F36" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G36" t="n">
-        <v>1.030553325744022e-09</v>
+        <v>2.094552332753774e-09</v>
       </c>
       <c r="H36" t="n">
-        <v>1.372779842211856e-06</v>
+        <v>2.561414312955196e-06</v>
       </c>
       <c r="I36" t="n">
         <v>-1.090780999152582</v>
@@ -2301,44 +2301,58 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GRB2</t>
+          <t>KIF18A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GRB2 (2885)</t>
+          <t>KIF18A (81930)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>liver</t>
+          <t>head and neck</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-1.656290751490781</v>
+        <v>-1.925937212164866</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.6760896204391904</v>
+        <v>-0.6696774587666032</v>
       </c>
       <c r="F37" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="G37" t="n">
-        <v>7.242410413832006e-05</v>
+        <v>0.0003994172358608</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0151545152436302</v>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+        <v>0.0489112905634394</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-0.8160878040287975</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.1818524073044841</v>
+      </c>
+      <c r="K37" t="n">
+        <v>34</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.8114412086085991</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.9999999999999653</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>not testable</t>
+          <t>not significant</t>
         </is>
       </c>
     </row>
@@ -2362,16 +2376,16 @@
         <v>-1.05165216366317</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.6675254179757004</v>
+        <v>-0.6691785166175629</v>
       </c>
       <c r="F38" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G38" t="n">
-        <v>3.664178220369402e-09</v>
+        <v>2.047223243448628e-08</v>
       </c>
       <c r="H38" t="n">
-        <v>4.120626190187731e-06</v>
+        <v>1.916933330710237e-05</v>
       </c>
       <c r="I38" t="n">
         <v>-0.4725346600730071</v>
@@ -2420,16 +2434,16 @@
         <v>-1.884925597357834</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.6564472035679869</v>
+        <v>-0.6676983149950186</v>
       </c>
       <c r="F39" t="n">
         <v>84</v>
       </c>
       <c r="G39" t="n">
-        <v>8.744000112119184e-09</v>
+        <v>4.709796938439963e-09</v>
       </c>
       <c r="H39" t="n">
-        <v>8.935230196762997e-06</v>
+        <v>5.256873326458903e-06</v>
       </c>
       <c r="I39" t="n">
         <v>-1.043152162195652</v>
@@ -2461,33 +2475,33 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TYMS</t>
+          <t>GRB2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TYMS (7298)</t>
+          <t>GRB2 (2885)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>myeloid</t>
+          <t>liver</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-1.15433161067098</v>
+        <v>-1.656290751490781</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.654135219920275</v>
+        <v>-0.6612071946411596</v>
       </c>
       <c r="F40" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0002141678858438</v>
+        <v>9.36957816962858e-05</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0317302377285973</v>
+        <v>0.0186255521156091</v>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
@@ -2505,160 +2519,146 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ATP1A1</t>
+          <t>TYMS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ATP1A1 (476)</t>
+          <t>TYMS (7298)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>breast</t>
+          <t>myeloid</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-1.869037534137749</v>
+        <v>-1.15433161067098</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.6483133747626586</v>
+        <v>-0.6521495546925569</v>
       </c>
       <c r="F41" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="G41" t="n">
-        <v>1.060652723263533e-06</v>
+        <v>0.0002078419412844</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0005539391892947</v>
-      </c>
-      <c r="I41" t="n">
-        <v>-1.126752705383011</v>
-      </c>
-      <c r="J41" t="n">
-        <v>-0.2714354460894485</v>
-      </c>
-      <c r="K41" t="n">
-        <v>25</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0.0477090274213294</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0.266934402927176</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
+        <v>0.0321665588651988</v>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>not significant</t>
+          <t>not testable</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SNAP23</t>
+          <t>ADSL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SNAP23 (8773)</t>
+          <t>ADSL (158)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>pleura</t>
+          <t>lymphoid</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-1.400290787875175</v>
+        <v>-1.538512362674913</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.6465158174240248</v>
+        <v>-0.65178098073852</v>
       </c>
       <c r="F42" t="n">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="G42" t="n">
-        <v>3.681434840633584e-05</v>
+        <v>3.094778731158322e-21</v>
       </c>
       <c r="H42" t="n">
-        <v>0.0093887915927973</v>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
+        <v>3.378434072471001e-17</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-1.142496695046854</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-0.5655240926018783</v>
+      </c>
+      <c r="K42" t="n">
+        <v>10</v>
+      </c>
+      <c r="L42" t="n">
+        <v>3.01803461920318e-05</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.0025433072428985</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1</v>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>not testable</t>
+          <t>meets rule</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ADSL</t>
+          <t>SNAP23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ADSL (158)</t>
+          <t>SNAP23 (8773)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>lymphoid</t>
+          <t>pleura</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-1.538512362674913</v>
+        <v>-1.400290787875175</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.6447502905518621</v>
+        <v>-0.6508933718761025</v>
       </c>
       <c r="F43" t="n">
-        <v>84</v>
+        <v>20</v>
       </c>
       <c r="G43" t="n">
-        <v>4.437524958730922e-21</v>
+        <v>3.375043631632447e-05</v>
       </c>
       <c r="H43" t="n">
-        <v>4.728911865485303e-17</v>
-      </c>
-      <c r="I43" t="n">
-        <v>-1.142496695046854</v>
-      </c>
-      <c r="J43" t="n">
-        <v>-0.5655240926018783</v>
-      </c>
-      <c r="K43" t="n">
-        <v>10</v>
-      </c>
-      <c r="L43" t="n">
-        <v>3.01803461920318e-05</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0.0025433072428985</v>
-      </c>
-      <c r="N43" t="n">
-        <v>1</v>
-      </c>
-      <c r="O43" t="n">
-        <v>1</v>
-      </c>
+        <v>0.008880650520884201</v>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>meets rule</t>
+          <t>not testable</t>
         </is>
       </c>
     </row>
@@ -2682,16 +2682,16 @@
         <v>-1.061582523443958</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.6428375742559935</v>
+        <v>-0.6460271482076028</v>
       </c>
       <c r="F44" t="n">
         <v>84</v>
       </c>
       <c r="G44" t="n">
-        <v>3.98473796507118e-28</v>
+        <v>1.76682639376993e-28</v>
       </c>
       <c r="H44" t="n">
-        <v>1.486237528057162e-23</v>
+        <v>7.907943904971515e-24</v>
       </c>
       <c r="I44" t="n">
         <v>-1.102053493567327</v>
@@ -2743,13 +2743,13 @@
         <v>-0.6345349103939644</v>
       </c>
       <c r="F45" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G45" t="n">
-        <v>2.435321209496469e-05</v>
+        <v>4.35698530828957e-05</v>
       </c>
       <c r="H45" t="n">
-        <v>0.0068789802124437</v>
+        <v>0.0107206988856456</v>
       </c>
       <c r="I45" t="n">
         <v>-1.397863999829573</v>
@@ -2804,10 +2804,10 @@
         <v>84</v>
       </c>
       <c r="G46" t="n">
-        <v>1.886680171802825e-18</v>
+        <v>1.869635701423777e-18</v>
       </c>
       <c r="H46" t="n">
-        <v>1.223823803790343e-14</v>
+        <v>1.230602467069931e-14</v>
       </c>
       <c r="I46" t="n">
         <v>-0.8666445785491204</v>
@@ -2856,16 +2856,16 @@
         <v>-1.17965095766039</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.6088547188610236</v>
+        <v>-0.609774122900838</v>
       </c>
       <c r="F47" t="n">
         <v>84</v>
       </c>
       <c r="G47" t="n">
-        <v>4.887987055085603e-28</v>
+        <v>8.177099405917845e-28</v>
       </c>
       <c r="H47" t="n">
-        <v>1.682892583175507e-23</v>
+        <v>3.049914979167753e-23</v>
       </c>
       <c r="I47" t="n">
         <v>-1.291651544721506</v>
@@ -2897,12 +2897,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TFRC</t>
+          <t>SDHB</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TFRC (7037)</t>
+          <t>SDHB (6390)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2911,19 +2911,19 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-1.487308219168991</v>
+        <v>-1.001921012931471</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.6029963754797887</v>
+        <v>-0.6085127516491038</v>
       </c>
       <c r="F48" t="n">
         <v>41</v>
       </c>
       <c r="G48" t="n">
-        <v>2.572307942263575e-09</v>
+        <v>1.856223333591821e-11</v>
       </c>
       <c r="H48" t="n">
-        <v>3.045796339921663e-06</v>
+        <v>3.924242660003469e-08</v>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
@@ -2941,70 +2941,56 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FPGS</t>
+          <t>TFRC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FPGS (2356)</t>
+          <t>TFRC (7037)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>lymphoid</t>
+          <t>myeloid</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-1.022338905434691</v>
+        <v>-1.487308219168991</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.6019724466018948</v>
+        <v>-0.6066716129543169</v>
       </c>
       <c r="F49" t="n">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="G49" t="n">
-        <v>7.267071659947307e-24</v>
+        <v>2.709143592860872e-09</v>
       </c>
       <c r="H49" t="n">
-        <v>1.355245277703148e-19</v>
-      </c>
-      <c r="I49" t="n">
-        <v>-1.104289869810222</v>
-      </c>
-      <c r="J49" t="n">
-        <v>-0.7703049738646378</v>
-      </c>
-      <c r="K49" t="n">
-        <v>10</v>
-      </c>
-      <c r="L49" t="n">
-        <v>2.977014010367525e-07</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0.0001654303785453</v>
-      </c>
-      <c r="N49" t="n">
-        <v>1</v>
-      </c>
-      <c r="O49" t="n">
-        <v>1</v>
-      </c>
+        <v>3.199355620446112e-06</v>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>meets rule</t>
+          <t>not testable</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FAM50A</t>
+          <t>FPGS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FAM50A (9130)</t>
+          <t>FPGS (2356)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3013,121 +2999,135 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-1.085693094648054</v>
+        <v>-1.022338905434691</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.6002126043596276</v>
+        <v>-0.6045900111892679</v>
       </c>
       <c r="F50" t="n">
         <v>84</v>
       </c>
       <c r="G50" t="n">
-        <v>7.668798726098083e-07</v>
+        <v>6.047095998690122e-24</v>
       </c>
       <c r="H50" t="n">
-        <v>0.0004242760525374</v>
+        <v>1.127730491665719e-19</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.7574073171122139</v>
+        <v>-1.104289869810222</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.5127810681254248</v>
+        <v>-0.7703049738646378</v>
       </c>
       <c r="K50" t="n">
         <v>10</v>
       </c>
       <c r="L50" t="n">
-        <v>0.0005736346832976</v>
+        <v>2.977014010367525e-07</v>
       </c>
       <c r="M50" t="n">
-        <v>0.0161242682962741</v>
+        <v>0.0001654303785453</v>
       </c>
       <c r="N50" t="n">
         <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>significant, below rule</t>
+          <t>meets rule</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SDHB</t>
+          <t>FAM50A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SDHB (6390)</t>
+          <t>FAM50A (9130)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>myeloid</t>
+          <t>lymphoid</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-1.001921012931471</v>
+        <v>-1.085693094648054</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.5990627487169113</v>
+        <v>-0.6002126043596276</v>
       </c>
       <c r="F51" t="n">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="G51" t="n">
-        <v>2.258364227470625e-11</v>
+        <v>7.249793285135909e-07</v>
       </c>
       <c r="H51" t="n">
-        <v>4.594529102577612e-08</v>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+        <v>0.000415474421097</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-0.7574073171122139</v>
+      </c>
+      <c r="J51" t="n">
+        <v>-0.5127810681254248</v>
+      </c>
+      <c r="K51" t="n">
+        <v>10</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.0005736346832976</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.0161242682962741</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>not testable</t>
+          <t>significant, below rule</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TRPM7</t>
+          <t>FERMT2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TRPM7 (54822)</t>
+          <t>FERMT2 (10979)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>myeloid</t>
+          <t>soft tissue</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-1.221545915323602</v>
+        <v>-1.119503264268766</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.5962524712713122</v>
+        <v>-0.5974689011488851</v>
       </c>
       <c r="F52" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G52" t="n">
-        <v>2.308707404210737e-10</v>
+        <v>5.039082390514072e-07</v>
       </c>
       <c r="H52" t="n">
-        <v>3.664287061238431e-07</v>
+        <v>0.0003106594293751</v>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
@@ -3145,33 +3145,33 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FERMT2</t>
+          <t>TRPM7</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FERMT2 (10979)</t>
+          <t>TRPM7 (54822)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>soft tissue</t>
+          <t>myeloid</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>-1.119503264268766</v>
+        <v>-1.221545915323602</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.5926607171523635</v>
+        <v>-0.5962524712713122</v>
       </c>
       <c r="F53" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G53" t="n">
-        <v>4.779815236965001e-07</v>
+        <v>2.28509342901043e-10</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0002893132626016</v>
+        <v>3.613992338738726e-07</v>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
@@ -3206,16 +3206,16 @@
         <v>-1.566429850753121</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.5926420905757489</v>
+        <v>-0.5862287197015303</v>
       </c>
       <c r="F54" t="n">
         <v>31</v>
       </c>
       <c r="G54" t="n">
-        <v>8.926346387301933e-07</v>
+        <v>1.300461279179651e-06</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0004842721442039</v>
+        <v>0.0006659715776589</v>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
@@ -3233,56 +3233,70 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ELOB</t>
+          <t>SCAP</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ELOB (6923)</t>
+          <t>SCAP (22937)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>cervix</t>
+          <t>bowel</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>-2.004145108267159</v>
+        <v>-1.523692860947368</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.5671855278829783</v>
+        <v>-0.5716833590187955</v>
       </c>
       <c r="F55" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G55" t="n">
-        <v>5.179699521525981e-06</v>
+        <v>9.13384955332529e-05</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0020106892733261</v>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
+        <v>0.0183241562045171</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-1.318253142819751</v>
+      </c>
+      <c r="J55" t="n">
+        <v>-0.5275865226078571</v>
+      </c>
+      <c r="K55" t="n">
+        <v>30</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.0001496146491405</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.0068273711531018</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1</v>
+      </c>
+      <c r="O55" t="n">
+        <v>1</v>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>not testable</t>
+          <t>meets rule</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>INTS6</t>
+          <t>NHLRC2</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>INTS6 (26512)</t>
+          <t>NHLRC2 (374354)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3291,19 +3305,19 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-1.396319646891632</v>
+        <v>-1.354483280162613</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.5636654021093819</v>
+        <v>-0.5683621080553867</v>
       </c>
       <c r="F56" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G56" t="n">
-        <v>3.866070520039796e-08</v>
+        <v>3.44516756409274e-09</v>
       </c>
       <c r="H56" t="n">
-        <v>3.321251395947969e-05</v>
+        <v>3.943694765138273e-06</v>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
@@ -3321,91 +3335,77 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RAB6A</t>
+          <t>ELOB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RAB6A (5870)</t>
+          <t>ELOB (6923)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>pancreas</t>
+          <t>cervix</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>-1.017651976331901</v>
+        <v>-2.004145108267159</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.5604934630167189</v>
+        <v>-0.5650579904840343</v>
       </c>
       <c r="F57" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G57" t="n">
-        <v>3.519487964553308e-05</v>
+        <v>5.565652881181656e-06</v>
       </c>
       <c r="H57" t="n">
-        <v>0.009074014422159001</v>
-      </c>
-      <c r="I57" t="n">
-        <v>-0.4223800340989483</v>
-      </c>
-      <c r="J57" t="n">
-        <v>-0.1007604754955774</v>
-      </c>
-      <c r="K57" t="n">
-        <v>23</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0.4481429904441463</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0.9435314245833279</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
+        <v>0.0021642652918387</v>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>not significant</t>
+          <t>not testable</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SEPHS2</t>
+          <t>DHFR</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SEPHS2 (22928)</t>
+          <t>DHFR (1719)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>myeloid</t>
+          <t>lymphoid</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>-1.294789951947827</v>
+        <v>-1.273802327287748</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.5577920735226907</v>
+        <v>-0.5603182364109947</v>
       </c>
       <c r="F58" t="n">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="G58" t="n">
-        <v>2.23185447135686e-05</v>
+        <v>8.050153933412077e-19</v>
       </c>
       <c r="H58" t="n">
-        <v>0.0064239948066587</v>
+        <v>5.811419108649426e-15</v>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
@@ -3440,16 +3440,16 @@
         <v>-1.005616970228762</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.5569823962311936</v>
+        <v>-0.5590509717882922</v>
       </c>
       <c r="F59" t="n">
         <v>41</v>
       </c>
       <c r="G59" t="n">
-        <v>1.196702085273529e-09</v>
+        <v>8.991990787432482e-10</v>
       </c>
       <c r="H59" t="n">
-        <v>1.566136615861523e-06</v>
+        <v>1.212063833928408e-06</v>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
@@ -3467,190 +3467,218 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>UROD</t>
+          <t>MED1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>UROD (7389)</t>
+          <t>MED1 (5469)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>lymphoid</t>
+          <t>myeloid</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>-1.063319948759066</v>
+        <v>-1.228344299228768</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.5565204289985366</v>
+        <v>-0.5572949443334795</v>
       </c>
       <c r="F60" t="n">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="G60" t="n">
-        <v>4.837830768459892e-19</v>
+        <v>1.431173614761198e-09</v>
       </c>
       <c r="H60" t="n">
-        <v>3.549690913961492e-15</v>
-      </c>
-      <c r="I60" t="n">
-        <v>-1.356625997696469</v>
-      </c>
-      <c r="J60" t="n">
-        <v>-0.6279951107005773</v>
-      </c>
-      <c r="K60" t="n">
-        <v>10</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0.0007510008830069</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0.019200816655012</v>
-      </c>
-      <c r="N60" t="n">
-        <v>1</v>
-      </c>
-      <c r="O60" t="n">
-        <v>1</v>
-      </c>
+        <v>1.830180729489149e-06</v>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>meets rule</t>
+          <t>not testable</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DHFR</t>
+          <t>RAB6A</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DHFR (1719)</t>
+          <t>RAB6A (5870)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>lymphoid</t>
+          <t>pancreas</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>-1.273802327287748</v>
+        <v>-1.017651976331901</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.554971609039457</v>
+        <v>-0.5555363152909762</v>
       </c>
       <c r="F61" t="n">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="G61" t="n">
-        <v>1.201721269217974e-18</v>
+        <v>1.800316170841468e-05</v>
       </c>
       <c r="H61" t="n">
-        <v>7.909782411107524e-15</v>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
+        <v>0.0055686503899727</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-0.4223800340989483</v>
+      </c>
+      <c r="J61" t="n">
+        <v>-0.1007604754955774</v>
+      </c>
+      <c r="K61" t="n">
+        <v>23</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.4481429904441463</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.9435314245833279</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>not testable</t>
+          <t>not significant</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MED1</t>
+          <t>UROD</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MED1 (5469)</t>
+          <t>UROD (7389)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>myeloid</t>
+          <t>lymphoid</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>-1.228344299228768</v>
+        <v>-1.063319948759066</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.5514324040065232</v>
+        <v>-0.555194939516346</v>
       </c>
       <c r="F62" t="n">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="G62" t="n">
-        <v>1.567006217758918e-09</v>
+        <v>3.537130550211627e-19</v>
       </c>
       <c r="H62" t="n">
-        <v>1.975659368840335e-06</v>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
+        <v>2.729560956091672e-15</v>
+      </c>
+      <c r="I62" t="n">
+        <v>-1.356625997696469</v>
+      </c>
+      <c r="J62" t="n">
+        <v>-0.6279951107005773</v>
+      </c>
+      <c r="K62" t="n">
+        <v>10</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.0007510008830069</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.019200816655012</v>
+      </c>
+      <c r="N62" t="n">
+        <v>1</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1</v>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>not testable</t>
+          <t>meets rule</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CKS1B</t>
+          <t>BUB3</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CKS1B (1163)</t>
+          <t>BUB3 (9184)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>cervix</t>
+          <t>head and neck</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>-1.252704173171887</v>
+        <v>-3.191064392170044</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.5440469271664343</v>
+        <v>-0.5522844436758021</v>
       </c>
       <c r="F63" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="G63" t="n">
-        <v>1.650444163913483e-07</v>
+        <v>1.116028741012876e-08</v>
       </c>
       <c r="H63" t="n">
-        <v>0.0001159661143548</v>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
+        <v>1.135252336076823e-05</v>
+      </c>
+      <c r="I63" t="n">
+        <v>-1.803468606301711</v>
+      </c>
+      <c r="J63" t="n">
+        <v>-0.1147735878845481</v>
+      </c>
+      <c r="K63" t="n">
+        <v>34</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.0123424342475954</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.1155357732410299</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>not testable</t>
+          <t>not significant</t>
         </is>
       </c>
     </row>
@@ -3674,16 +3702,16 @@
         <v>-1.540676236530749</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.5423622730601331</v>
+        <v>-0.5452268213664281</v>
       </c>
       <c r="F64" t="n">
         <v>41</v>
       </c>
       <c r="G64" t="n">
-        <v>1.265620531735028e-05</v>
+        <v>1.07932241437636e-05</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0041284586733647</v>
+        <v>0.0036932878203681</v>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
@@ -3701,318 +3729,318 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CRKL</t>
+          <t>CKS1B</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CRKL (1399)</t>
+          <t>CKS1B (1163)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>pancreas</t>
+          <t>cervix</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>-1.328961830708118</v>
+        <v>-1.252704173171887</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.5411464270318499</v>
+        <v>-0.5428871644383437</v>
       </c>
       <c r="F65" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0001972745374144</v>
+        <v>1.670998750509784e-07</v>
       </c>
       <c r="H65" t="n">
-        <v>0.0299612962950256</v>
-      </c>
-      <c r="I65" t="n">
-        <v>-0.8425327301947045</v>
-      </c>
-      <c r="J65" t="n">
-        <v>-0.1914368888415086</v>
-      </c>
-      <c r="K65" t="n">
-        <v>23</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0.008611042947851401</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0.0922326833377513</v>
-      </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
+        <v>0.000120241792565</v>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>not significant</t>
+          <t>not testable</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BUB3</t>
+          <t>SEPHS2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BUB3 (9184)</t>
+          <t>SEPHS2 (22928)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>head and neck</t>
+          <t>myeloid</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>-3.180179819882502</v>
+        <v>-1.294789951947827</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.5387358748436029</v>
+        <v>-0.5418257401540657</v>
       </c>
       <c r="F66" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G66" t="n">
-        <v>8.961976279784771e-09</v>
+        <v>2.694531159904477e-05</v>
       </c>
       <c r="H66" t="n">
-        <v>9.116346321204062e-06</v>
-      </c>
-      <c r="I66" t="n">
-        <v>-1.803468606301711</v>
-      </c>
-      <c r="J66" t="n">
-        <v>-0.1147735878845481</v>
-      </c>
-      <c r="K66" t="n">
-        <v>34</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0.0123424342475954</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0.1155357732410299</v>
-      </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" t="n">
-        <v>0</v>
-      </c>
+        <v>0.0075179236778412</v>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>not significant</t>
+          <t>not testable</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AP2S1</t>
+          <t>CCND1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AP2S1 (1175)</t>
+          <t>CCND1 (595)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>myeloid</t>
+          <t>head and neck</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>-1.302407584499616</v>
+        <v>-1.55354269135501</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.5323682255846232</v>
+        <v>-0.5334336065738179</v>
       </c>
       <c r="F67" t="n">
         <v>41</v>
       </c>
       <c r="G67" t="n">
-        <v>2.08319001500732e-11</v>
+        <v>0.0001127819711979</v>
       </c>
       <c r="H67" t="n">
-        <v>4.296737805193369e-08</v>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
+        <v>0.0212652220569211</v>
+      </c>
+      <c r="I67" t="n">
+        <v>-0.6425432892608847</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.2514168375427243</v>
+      </c>
+      <c r="K67" t="n">
+        <v>34</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.9759264313710876</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.9999999999999653</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>not testable</t>
+          <t>not significant</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FAM50A</t>
+          <t>MYH9</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FAM50A (9130)</t>
+          <t>MYH9 (4627)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>myeloid</t>
+          <t>pancreas</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>-1.028369176843959</v>
+        <v>-1.04859007267901</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.5290211552613209</v>
+        <v>-0.5310013890202979</v>
       </c>
       <c r="F68" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0002399735353657</v>
+        <v>1.039788738494974e-06</v>
       </c>
       <c r="H68" t="n">
-        <v>0.034174674235439</v>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
+        <v>0.0005607392053365</v>
+      </c>
+      <c r="I68" t="n">
+        <v>-0.5711184817148458</v>
+      </c>
+      <c r="J68" t="n">
+        <v>-0.1194414503499939</v>
+      </c>
+      <c r="K68" t="n">
+        <v>23</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.0824364911300275</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.3701902414853865</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>not testable</t>
+          <t>not significant</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>UROD</t>
+          <t>FERMT2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>UROD (7389)</t>
+          <t>FERMT2 (10979)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>myeloid</t>
+          <t>ovary/fallopian tube</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>-1.059438818055799</v>
+        <v>-1.067771506055804</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.5275284761511621</v>
+        <v>-0.5298575917415111</v>
       </c>
       <c r="F69" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="G69" t="n">
-        <v>3.133544249793453e-08</v>
+        <v>2.51731050887229e-05</v>
       </c>
       <c r="H69" t="n">
-        <v>2.755419649859143e-05</v>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
+        <v>0.0071672730295836</v>
+      </c>
+      <c r="I69" t="n">
+        <v>-0.4610967125539306</v>
+      </c>
+      <c r="J69" t="n">
+        <v>-0.2036825766095725</v>
+      </c>
+      <c r="K69" t="n">
+        <v>29</v>
+      </c>
+      <c r="L69" t="n">
+        <v>5.716474901481154e-05</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.0037814291946974</v>
+      </c>
+      <c r="N69" t="n">
+        <v>1</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>not testable</t>
+          <t>significant, below rule</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SCAP</t>
+          <t>FAM50A</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SCAP (22937)</t>
+          <t>FAM50A (9130)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>bowel</t>
+          <t>myeloid</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>-1.476376337528556</v>
+        <v>-1.028369176843959</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.5258874039598401</v>
+        <v>-0.5290211552613209</v>
       </c>
       <c r="F70" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G70" t="n">
-        <v>6.24137748673735e-05</v>
+        <v>0.0002280275215819</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0136335260816808</v>
-      </c>
-      <c r="I70" t="n">
-        <v>-1.318253142819751</v>
-      </c>
-      <c r="J70" t="n">
-        <v>-0.5275865226078571</v>
-      </c>
-      <c r="K70" t="n">
-        <v>30</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0.0001496146491405</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0.0068273711531018</v>
-      </c>
-      <c r="N70" t="n">
-        <v>1</v>
-      </c>
-      <c r="O70" t="n">
-        <v>1</v>
-      </c>
+        <v>0.0342254628041966</v>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>meets rule</t>
+          <t>not testable</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DNM2</t>
+          <t>AP2S1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DNM2 (1785)</t>
+          <t>AP2S1 (1175)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4021,19 +4049,19 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>-1.69167040036456</v>
+        <v>-1.302407584499616</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.5240646762003673</v>
+        <v>-0.5265208469433831</v>
       </c>
       <c r="F71" t="n">
         <v>41</v>
       </c>
       <c r="G71" t="n">
-        <v>7.540285125006614e-14</v>
+        <v>2.464819331046768e-11</v>
       </c>
       <c r="H71" t="n">
-        <v>2.427966385586572e-10</v>
+        <v>5.083877287422035e-08</v>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
@@ -4051,116 +4079,88 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MYH9</t>
+          <t>UROD</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MYH9 (4627)</t>
+          <t>UROD (7389)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>pancreas</t>
+          <t>myeloid</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>-1.040519776306158</v>
+        <v>-1.059438818055799</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.523753387891545</v>
+        <v>-0.521998747401327</v>
       </c>
       <c r="F72" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="G72" t="n">
-        <v>1.480810504717361e-06</v>
+        <v>2.882082920825214e-08</v>
       </c>
       <c r="H72" t="n">
-        <v>0.0007283293240559</v>
-      </c>
-      <c r="I72" t="n">
-        <v>-0.5711184817148458</v>
-      </c>
-      <c r="J72" t="n">
-        <v>-0.1194414503499939</v>
-      </c>
-      <c r="K72" t="n">
-        <v>23</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0.0824364911300275</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0.3701902414853865</v>
-      </c>
-      <c r="N72" t="n">
-        <v>0</v>
-      </c>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
+        <v>2.579919583240058e-05</v>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>not significant</t>
+          <t>not testable</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CCND1</t>
+          <t>DNM2</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CCND1 (595)</t>
+          <t>DNM2 (1785)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>head and neck</t>
+          <t>myeloid</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>-1.541487161304006</v>
+        <v>-1.69167040036456</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.5201294007454789</v>
+        <v>-0.5205004817451246</v>
       </c>
       <c r="F73" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0003819024011111</v>
+        <v>8.53680477199422e-14</v>
       </c>
       <c r="H73" t="n">
-        <v>0.0457158317162165</v>
-      </c>
-      <c r="I73" t="n">
-        <v>-0.6425432892608847</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0.2514168375427243</v>
-      </c>
-      <c r="K73" t="n">
-        <v>34</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0.9759264313710876</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0.9999999999999653</v>
-      </c>
-      <c r="N73" t="n">
-        <v>0</v>
-      </c>
-      <c r="O73" t="n">
-        <v>0</v>
-      </c>
+        <v>2.690770804960845e-10</v>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>not significant</t>
+          <t>not testable</t>
         </is>
       </c>
     </row>
@@ -4190,10 +4190,10 @@
         <v>41</v>
       </c>
       <c r="G74" t="n">
-        <v>1.30781957728501e-09</v>
+        <v>1.381187828936837e-09</v>
       </c>
       <c r="H74" t="n">
-        <v>1.686895039140194e-06</v>
+        <v>1.779390686367688e-06</v>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
@@ -4211,33 +4211,33 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PTK2</t>
+          <t>INTS6</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PTK2 (5747)</t>
+          <t>INTS6 (26512)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>liver</t>
+          <t>skin</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>-1.054139446371316</v>
+        <v>-1.346559113584217</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.5167185017318694</v>
+        <v>-0.5147951748550157</v>
       </c>
       <c r="F75" t="n">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="G75" t="n">
-        <v>4.704365838096124e-05</v>
+        <v>2.247217297422159e-07</v>
       </c>
       <c r="H75" t="n">
-        <v>0.0111053552608081</v>
+        <v>0.0001556977199323</v>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
@@ -4255,58 +4255,44 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PPP1R15B</t>
+          <t>PTK2</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PPP1R15B (84919)</t>
+          <t>PTK2 (5747)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>breast</t>
+          <t>liver</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>-1.290228427684214</v>
+        <v>-1.054139446371316</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.5150081318669822</v>
+        <v>-0.5130590587252496</v>
       </c>
       <c r="F76" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G76" t="n">
-        <v>6.719337958986104e-05</v>
+        <v>5.295404049005589e-05</v>
       </c>
       <c r="H76" t="n">
-        <v>0.014375882238743</v>
-      </c>
-      <c r="I76" t="n">
-        <v>-0.687776789923331</v>
-      </c>
-      <c r="J76" t="n">
-        <v>-0.1655918878044298</v>
-      </c>
-      <c r="K76" t="n">
-        <v>25</v>
-      </c>
-      <c r="L76" t="n">
-        <v>0.0063698842352664</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0.0762947798672273</v>
-      </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
+        <v>0.0122965115969223</v>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>not significant</t>
+          <t>not testable</t>
         </is>
       </c>
     </row>
@@ -4330,16 +4316,16 @@
         <v>-1.667128592661345</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.5127867146427008</v>
+        <v>-0.5089987898773374</v>
       </c>
       <c r="F77" t="n">
         <v>84</v>
       </c>
       <c r="G77" t="n">
-        <v>2.478058704959177e-23</v>
+        <v>3.010575391048264e-23</v>
       </c>
       <c r="H77" t="n">
-        <v>3.824575990023873e-19</v>
+        <v>4.491567743166637e-19</v>
       </c>
       <c r="I77" t="n">
         <v>-1.340018094656139</v>
@@ -4365,166 +4351,6 @@
       <c r="P77" t="inlineStr">
         <is>
           <t>not significant</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>FERMT2</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>FERMT2 (10979)</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>ovary/fallopian tube</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>-1.050899938523135</v>
-      </c>
-      <c r="E78" t="n">
-        <v>-0.5121968458560141</v>
-      </c>
-      <c r="F78" t="n">
-        <v>31</v>
-      </c>
-      <c r="G78" t="n">
-        <v>3.558502989366651e-05</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0.0091482550802856</v>
-      </c>
-      <c r="I78" t="n">
-        <v>-0.4610967125539306</v>
-      </c>
-      <c r="J78" t="n">
-        <v>-0.2036825766095725</v>
-      </c>
-      <c r="K78" t="n">
-        <v>29</v>
-      </c>
-      <c r="L78" t="n">
-        <v>5.716474901481154e-05</v>
-      </c>
-      <c r="M78" t="n">
-        <v>0.0037814291946974</v>
-      </c>
-      <c r="N78" t="n">
-        <v>1</v>
-      </c>
-      <c r="O78" t="n">
-        <v>0</v>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>significant, below rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>NHLRC2</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>NHLRC2 (374354)</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>skin</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>-1.288449593278653</v>
-      </c>
-      <c r="E79" t="n">
-        <v>-0.5008059487351257</v>
-      </c>
-      <c r="F79" t="n">
-        <v>71</v>
-      </c>
-      <c r="G79" t="n">
-        <v>4.147786944698988e-08</v>
-      </c>
-      <c r="H79" t="n">
-        <v>3.522698923949579e-05</v>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>not testable</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>GRB2</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>GRB2 (2885)</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>head and neck</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>-1.474191718246479</v>
-      </c>
-      <c r="E80" t="n">
-        <v>-0.5004788604295689</v>
-      </c>
-      <c r="F80" t="n">
-        <v>42</v>
-      </c>
-      <c r="G80" t="n">
-        <v>6.724724417621728e-06</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0.0024683274903745</v>
-      </c>
-      <c r="I80" t="n">
-        <v>-1.012981896786246</v>
-      </c>
-      <c r="J80" t="n">
-        <v>-0.3568471092676095</v>
-      </c>
-      <c r="K80" t="n">
-        <v>34</v>
-      </c>
-      <c r="L80" t="n">
-        <v>1.867068369774268e-08</v>
-      </c>
-      <c r="M80" t="n">
-        <v>4.175254393929171e-05</v>
-      </c>
-      <c r="N80" t="n">
-        <v>1</v>
-      </c>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>significant, below rule</t>
         </is>
       </c>
     </row>
@@ -4653,16 +4479,16 @@
         <v>3.187197196705966e-18</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.383151857934958</v>
+        <v>-1.355846247765565</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.888434536504414</v>
+        <v>-1.86019184995362</v>
       </c>
       <c r="J2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K2" t="n">
-        <v>5.03582747120326e-09</v>
+        <v>5.381075368454397e-08</v>
       </c>
       <c r="L2" t="n">
         <v>-0.9075659555254312</v>
@@ -4709,16 +4535,16 @@
         <v>1.564370931631922e-25</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.378311916898018</v>
+        <v>-1.374373056890616</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.670209320059542</v>
+        <v>-1.665313946694566</v>
       </c>
       <c r="J3" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K3" t="n">
-        <v>3.237469519866092e-24</v>
+        <v>4.646380622276572e-23</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -4757,7 +4583,7 @@
         <v>1.061594244485153e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.151555296152607</v>
+        <v>-1.153061180935798</v>
       </c>
       <c r="I4" t="n">
         <v>-1.309117850188102</v>
@@ -4766,7 +4592,7 @@
         <v>31</v>
       </c>
       <c r="K4" t="n">
-        <v>4.167726428633955e-06</v>
+        <v>3.858182434277223e-06</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -4845,7 +4671,7 @@
         <v>0.0018629450660217</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.123606136150321</v>
+        <v>-1.122754221813722</v>
       </c>
       <c r="I6" t="n">
         <v>-1.55427191249818</v>
@@ -4854,7 +4680,7 @@
         <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0047464666938756</v>
+        <v>0.0048004267801007</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -4893,16 +4719,16 @@
         <v>2.002386607517575e-21</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9155821860809426</v>
+        <v>-0.8130451982129844</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.050836261465989</v>
+        <v>-0.948097404406016</v>
       </c>
       <c r="J7" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K7" t="n">
-        <v>6.340801206176097e-08</v>
+        <v>5.553379665705373e-07</v>
       </c>
       <c r="L7" t="n">
         <v>-0.7986913477094655</v>
@@ -4917,7 +4743,7 @@
         <v>2.948932717146128e-10</v>
       </c>
       <c r="P7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4949,7 +4775,7 @@
         <v>7.369140799508597e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.152487627196181</v>
+        <v>-1.14941003313538</v>
       </c>
       <c r="I8" t="n">
         <v>-1.715027919050082</v>
@@ -4958,7 +4784,7 @@
         <v>31</v>
       </c>
       <c r="K8" t="n">
-        <v>8.720191712606542e-06</v>
+        <v>9.793822586424351e-06</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
@@ -4997,7 +4823,7 @@
         <v>1.993415021868269e-21</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.057744111463523</v>
+        <v>-1.056202281613122</v>
       </c>
       <c r="I9" t="n">
         <v>-1.356473385502453</v>
@@ -5006,7 +4832,7 @@
         <v>41</v>
       </c>
       <c r="K9" t="n">
-        <v>2.055994094089369e-19</v>
+        <v>2.094094291521859e-19</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -5045,7 +4871,7 @@
         <v>3.7527856318775e-17</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.027249340913516</v>
+        <v>-1.028137366834277</v>
       </c>
       <c r="I10" t="n">
         <v>-1.181373370396734</v>
@@ -5054,7 +4880,7 @@
         <v>41</v>
       </c>
       <c r="K10" t="n">
-        <v>6.350751401432671e-15</v>
+        <v>8.378020895432347e-15</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
@@ -5093,7 +4919,7 @@
         <v>0.0498215935764428</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.042843222563416</v>
+        <v>-1.04575026563261</v>
       </c>
       <c r="I11" t="n">
         <v>-1.371058348815747</v>
@@ -5102,7 +4928,7 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0782693464953442</v>
+        <v>0.078365059847394</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
@@ -5141,7 +4967,7 @@
         <v>1.069308460837993e-10</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.812286005416411</v>
+        <v>-0.813442742098627</v>
       </c>
       <c r="I12" t="n">
         <v>-0.920597475560844</v>
@@ -5150,7 +4976,7 @@
         <v>31</v>
       </c>
       <c r="K12" t="n">
-        <v>6.948061448834352e-09</v>
+        <v>5.721501713873427e-09</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
@@ -5189,16 +5015,16 @@
         <v>2.865245816978804e-20</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.027559895688165</v>
+        <v>-1.037382726441304</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.097895688783254</v>
+        <v>-1.108464193096825</v>
       </c>
       <c r="J13" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K13" t="n">
-        <v>1.326625974803198e-18</v>
+        <v>2.823620773483398e-17</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
@@ -5237,7 +5063,7 @@
         <v>5.995325291161477e-07</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.9790511831748312</v>
+        <v>-0.979158079276144</v>
       </c>
       <c r="I14" t="n">
         <v>-1.101619065138771</v>
@@ -5246,7 +5072,7 @@
         <v>18</v>
       </c>
       <c r="K14" t="n">
-        <v>1.01411951133957e-06</v>
+        <v>1.014847383858619e-06</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
@@ -5285,7 +5111,7 @@
         <v>1.788074309446857e-35</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9377736274129606</v>
+        <v>-0.9375967736472</v>
       </c>
       <c r="I15" t="n">
         <v>-1.174440146267304</v>
@@ -5294,7 +5120,7 @@
         <v>84</v>
       </c>
       <c r="K15" t="n">
-        <v>1.872466421565998e-29</v>
+        <v>1.985614060067463e-29</v>
       </c>
       <c r="L15" t="n">
         <v>-0.6139955932501796</v>
@@ -5341,7 +5167,7 @@
         <v>1.291185267029882e-24</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8791366649076594</v>
+        <v>-0.8787703734173465</v>
       </c>
       <c r="I16" t="n">
         <v>-0.9746005345764756</v>
@@ -5350,7 +5176,7 @@
         <v>84</v>
       </c>
       <c r="K16" t="n">
-        <v>3.23554369755365e-20</v>
+        <v>4.604233561224322e-20</v>
       </c>
       <c r="L16" t="n">
         <v>-1.015325954131146</v>
@@ -5397,16 +5223,16 @@
         <v>4.688825006013575e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7615347765487575</v>
+        <v>-0.7620790366408952</v>
       </c>
       <c r="I17" t="n">
         <v>-1.781991279327073</v>
       </c>
       <c r="J17" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K17" t="n">
-        <v>0.015930487048031</v>
+        <v>0.0355449494842596</v>
       </c>
       <c r="L17" t="n">
         <v>-0.6187715502525587</v>
@@ -5453,7 +5279,7 @@
         <v>2.591116513538949e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8376090773763644</v>
+        <v>-0.8413289126046094</v>
       </c>
       <c r="I18" t="n">
         <v>-1.37473381333783</v>
@@ -5462,7 +5288,7 @@
         <v>31</v>
       </c>
       <c r="K18" t="n">
-        <v>6.519591885699882e-05</v>
+        <v>6.865279651483914e-05</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
@@ -5501,7 +5327,7 @@
         <v>0.0004526577441391</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.906106271680397</v>
+        <v>-0.9040173394232291</v>
       </c>
       <c r="I19" t="n">
         <v>-1.569685120222577</v>
@@ -5510,7 +5336,7 @@
         <v>18</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0007523144121187</v>
+        <v>0.0007889333361257</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
@@ -5549,7 +5375,7 @@
         <v>2.850614792621525e-06</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8639512744068607</v>
+        <v>-0.8636085924861948</v>
       </c>
       <c r="I20" t="n">
         <v>-1.290220009827672</v>
@@ -5558,7 +5384,7 @@
         <v>31</v>
       </c>
       <c r="K20" t="n">
-        <v>2.595233954448539e-05</v>
+        <v>2.480308591831672e-05</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
@@ -5597,7 +5423,7 @@
         <v>0.0051300113779324</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8440042486022828</v>
+        <v>-0.8431523342656835</v>
       </c>
       <c r="I21" t="n">
         <v>-1.274670024950142</v>
@@ -5606,7 +5432,7 @@
         <v>20</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0340569224518542</v>
+        <v>0.0347893031573204</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
@@ -5645,7 +5471,7 @@
         <v>0.0201086067033159</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8059917114552559</v>
+        <v>-0.8078855064342754</v>
       </c>
       <c r="I22" t="n">
         <v>-1.612606018434213</v>
@@ -5654,7 +5480,7 @@
         <v>11</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0406972598126226</v>
+        <v>0.0411459528511413</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
@@ -5693,16 +5519,16 @@
         <v>2.130793419975699e-07</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8293536033669171</v>
+        <v>-0.7756647224429027</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.252661993566242</v>
+        <v>-1.200210115640962</v>
       </c>
       <c r="J23" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K23" t="n">
-        <v>2.540925134630946e-06</v>
+        <v>1.896043740737577e-05</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -5750,7 +5576,7 @@
         <v>84</v>
       </c>
       <c r="K24" t="n">
-        <v>8.345695101032257e-30</v>
+        <v>1.295925381186712e-29</v>
       </c>
       <c r="L24" t="n">
         <v>-0.7683691542881097</v>
@@ -5797,7 +5623,7 @@
         <v>1.233334070113956e-07</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.8332535551178025</v>
+        <v>-0.8337962085417162</v>
       </c>
       <c r="I25" t="n">
         <v>-1.265894857139244</v>
@@ -5806,7 +5632,7 @@
         <v>41</v>
       </c>
       <c r="K25" t="n">
-        <v>3.303941548251352e-07</v>
+        <v>2.50265689311839e-07</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
@@ -5845,7 +5671,7 @@
         <v>0.0436684300205172</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.781613221530929</v>
+        <v>-0.7897284163714716</v>
       </c>
       <c r="I26" t="n">
         <v>-1.437407598292096</v>
@@ -5854,7 +5680,7 @@
         <v>7</v>
       </c>
       <c r="K26" t="n">
-        <v>0.089662780171267</v>
+        <v>0.0974531563189245</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
@@ -5893,7 +5719,7 @@
         <v>8.375583726715813e-28</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.7708568973920226</v>
+        <v>-0.770999423393094</v>
       </c>
       <c r="I27" t="n">
         <v>-1.057275251564049</v>
@@ -5902,7 +5728,7 @@
         <v>84</v>
       </c>
       <c r="K27" t="n">
-        <v>8.349741099423193e-25</v>
+        <v>9.704471594312507e-25</v>
       </c>
       <c r="L27" t="n">
         <v>-0.8320289078006696</v>
@@ -5955,10 +5781,10 @@
         <v>-1.383326730283341</v>
       </c>
       <c r="J28" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0068789802124437</v>
+        <v>0.0107206988856456</v>
       </c>
       <c r="L28" t="n">
         <v>-0.7623168675934182</v>
@@ -6005,7 +5831,7 @@
         <v>1.749642161596922e-24</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.772127397666838</v>
+        <v>-0.775405600373415</v>
       </c>
       <c r="I29" t="n">
         <v>-1.187649371045798</v>
@@ -6014,7 +5840,7 @@
         <v>84</v>
       </c>
       <c r="K29" t="n">
-        <v>1.624884877660683e-20</v>
+        <v>6.382986803894618e-21</v>
       </c>
       <c r="L29" t="n">
         <v>-0.4515675055507923</v>
@@ -6061,7 +5887,7 @@
         <v>0.0064358125316687</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.776882126008951</v>
+        <v>-0.7640439407303127</v>
       </c>
       <c r="I30" t="n">
         <v>-1.524245141524018</v>
@@ -6070,7 +5896,7 @@
         <v>31</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0129581020390396</v>
+        <v>0.0146069957419781</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
@@ -6109,7 +5935,7 @@
         <v>1.066329968488419e-18</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.7045009613477999</v>
+        <v>-0.6999576551205116</v>
       </c>
       <c r="I31" t="n">
         <v>-1.403718227685325</v>
@@ -6118,7 +5944,7 @@
         <v>84</v>
       </c>
       <c r="K31" t="n">
-        <v>1.174144166179649e-12</v>
+        <v>1.770787645613075e-12</v>
       </c>
       <c r="L31" t="n">
         <v>-0.6683619823193591</v>
@@ -6165,16 +5991,16 @@
         <v>6.567133377174271e-12</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.7068852699518278</v>
+        <v>-0.7114391449734631</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.206637670818067</v>
+        <v>-1.209017506087039</v>
       </c>
       <c r="J32" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K32" t="n">
-        <v>1.331963147820556e-09</v>
+        <v>1.895804412479045e-09</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
@@ -6213,7 +6039,7 @@
         <v>6.722873469486667e-22</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.733054603100721</v>
+        <v>-0.7378181744280528</v>
       </c>
       <c r="I33" t="n">
         <v>-1.575504219990485</v>
@@ -6222,7 +6048,7 @@
         <v>84</v>
       </c>
       <c r="K33" t="n">
-        <v>1.511412199259516e-18</v>
+        <v>1.77743939206016e-18</v>
       </c>
       <c r="L33" t="n">
         <v>-0.5093730207647554</v>
@@ -6269,7 +6095,7 @@
         <v>5.283245410562019e-11</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7452549194630895</v>
+        <v>-0.7451313727037595</v>
       </c>
       <c r="I34" t="n">
         <v>-1.04487301021957</v>
@@ -6278,7 +6104,7 @@
         <v>41</v>
       </c>
       <c r="K34" t="n">
-        <v>1.335487592668445e-10</v>
+        <v>1.4729503956248e-10</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -6317,7 +6143,7 @@
         <v>3.128360546731804e-25</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7703567180857969</v>
+        <v>-0.7745258960462706</v>
       </c>
       <c r="I35" t="n">
         <v>-1.143610907398437</v>
@@ -6326,7 +6152,7 @@
         <v>84</v>
       </c>
       <c r="K35" t="n">
-        <v>1.291257744808302e-21</v>
+        <v>8.47056953597791e-22</v>
       </c>
       <c r="L35" t="n">
         <v>-0.5952616989895489</v>
@@ -6373,7 +6199,7 @@
         <v>9.685569519877933e-08</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7447748873917154</v>
+        <v>-0.7458711036091752</v>
       </c>
       <c r="I36" t="n">
         <v>-1.694782825699614</v>
@@ -6382,7 +6208,7 @@
         <v>41</v>
       </c>
       <c r="K36" t="n">
-        <v>8.765435991019069e-08</v>
+        <v>8.340981389182286e-08</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
@@ -6421,16 +6247,16 @@
         <v>0.0001212204883906</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.747392356212476</v>
+        <v>-0.7595372716705364</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.751117706291526</v>
+        <v>-1.760862167813841</v>
       </c>
       <c r="J37" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K37" t="n">
-        <v>1.067374772572165e-05</v>
+        <v>7.587343566215078e-06</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
@@ -6517,7 +6343,7 @@
         <v>2.141754738374966e-13</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.7110288840300132</v>
+        <v>-0.7206873358025989</v>
       </c>
       <c r="I39" t="n">
         <v>-1.655886854258267</v>
@@ -6526,7 +6352,7 @@
         <v>84</v>
       </c>
       <c r="K39" t="n">
-        <v>5.074662491965958e-10</v>
+        <v>3.188340228055831e-10</v>
       </c>
       <c r="L39" t="n">
         <v>-0.539108158156004</v>
@@ -6573,7 +6399,7 @@
         <v>3.52692831213519e-28</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.6957377571731682</v>
+        <v>-0.6911036411122127</v>
       </c>
       <c r="I40" t="n">
         <v>-0.9696958536952948</v>
@@ -6582,7 +6408,7 @@
         <v>84</v>
       </c>
       <c r="K40" t="n">
-        <v>3.162537709263379e-23</v>
+        <v>3.878531753844611e-23</v>
       </c>
       <c r="L40" t="n">
         <v>-0.5553892515318426</v>
@@ -6629,16 +6455,16 @@
         <v>1.326641992528276e-07</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.7161270544452555</v>
+        <v>-0.7076766514895794</v>
       </c>
       <c r="I41" t="n">
         <v>-1.673854449943091</v>
       </c>
       <c r="J41" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K41" t="n">
-        <v>0.0002883233790696</v>
+        <v>0.0007332056847541</v>
       </c>
       <c r="L41" t="n">
         <v>-0.4931080971911801</v>
@@ -6685,16 +6511,16 @@
         <v>7.871437230639302e-11</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.6876945661074978</v>
+        <v>-0.6885124293263206</v>
       </c>
       <c r="I42" t="n">
         <v>-1.192344899201941</v>
       </c>
       <c r="J42" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K42" t="n">
-        <v>1.372779842211856e-06</v>
+        <v>2.561414312955196e-06</v>
       </c>
       <c r="L42" t="n">
         <v>-0.7388194911294765</v>
@@ -6750,7 +6576,7 @@
         <v>10</v>
       </c>
       <c r="K43" t="n">
-        <v>0.0178774386654746</v>
+        <v>0.0185171785654315</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
@@ -6789,7 +6615,7 @@
         <v>6.830417681619416e-19</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.6447502905518621</v>
+        <v>-0.65178098073852</v>
       </c>
       <c r="I44" t="n">
         <v>-1.538512362674913</v>
@@ -6798,7 +6624,7 @@
         <v>84</v>
       </c>
       <c r="K44" t="n">
-        <v>4.728911865485303e-17</v>
+        <v>3.378434072471001e-17</v>
       </c>
       <c r="L44" t="n">
         <v>-0.5655240926018783</v>
@@ -6845,7 +6671,7 @@
         <v>0.0061217129645757</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.6465158174240248</v>
+        <v>-0.6508933718761025</v>
       </c>
       <c r="I45" t="n">
         <v>-1.400290787875175</v>
@@ -6854,7 +6680,7 @@
         <v>20</v>
       </c>
       <c r="K45" t="n">
-        <v>0.0093887915927973</v>
+        <v>0.008880650520884201</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
@@ -6893,16 +6719,16 @@
         <v>2.85379597482887e-05</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.5258874039598401</v>
+        <v>-0.5716833590187955</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.476376337528556</v>
+        <v>-1.523692860947368</v>
       </c>
       <c r="J46" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K46" t="n">
-        <v>0.0136335260816808</v>
+        <v>0.0183241562045171</v>
       </c>
       <c r="L46" t="n">
         <v>-0.5275865226078571</v>
@@ -6949,7 +6775,7 @@
         <v>0.0013122480434529</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.3881690632870689</v>
+        <v>-0.3858937316373043</v>
       </c>
       <c r="I47" t="n">
         <v>-2.431461893651065</v>
@@ -6958,7 +6784,7 @@
         <v>8</v>
       </c>
       <c r="K47" t="n">
-        <v>0.4009676587504263</v>
+        <v>0.427607454094125</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
@@ -6997,16 +6823,16 @@
         <v>0.008480238132643101</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.32163575801924</v>
+        <v>-0.3177698335897652</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.8275271974162401</v>
+        <v>-0.8244599027838098</v>
       </c>
       <c r="J48" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K48" t="n">
-        <v>0.4965737694408798</v>
+        <v>0.6617365101422062</v>
       </c>
       <c r="L48" t="n">
         <v>-0.4575487738729497</v>
@@ -7053,7 +6879,7 @@
         <v>5.567374420538587e-24</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.6019724466018948</v>
+        <v>-0.6045900111892679</v>
       </c>
       <c r="I49" t="n">
         <v>-1.022338905434691</v>
@@ -7062,7 +6888,7 @@
         <v>84</v>
       </c>
       <c r="K49" t="n">
-        <v>1.355245277703148e-19</v>
+        <v>1.127730491665719e-19</v>
       </c>
       <c r="L49" t="n">
         <v>-0.7703049738646378</v>
@@ -7109,7 +6935,7 @@
         <v>1.037054157067516e-26</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.6428375742559935</v>
+        <v>-0.6460271482076028</v>
       </c>
       <c r="I50" t="n">
         <v>-1.061582523443958</v>
@@ -7118,7 +6944,7 @@
         <v>84</v>
       </c>
       <c r="K50" t="n">
-        <v>1.486237528057162e-23</v>
+        <v>7.907943904971515e-24</v>
       </c>
       <c r="L50" t="n">
         <v>-0.6265301413457973</v>
@@ -7165,7 +6991,7 @@
         <v>0.0131101973908288</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.654135219920275</v>
+        <v>-0.6521495546925569</v>
       </c>
       <c r="I51" t="n">
         <v>-1.15433161067098</v>
@@ -7174,7 +7000,7 @@
         <v>41</v>
       </c>
       <c r="K51" t="n">
-        <v>0.0317302377285973</v>
+        <v>0.0321665588651988</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
@@ -7213,7 +7039,7 @@
         <v>1.661505483851377e-05</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.5926607171523635</v>
+        <v>-0.5974689011488851</v>
       </c>
       <c r="I52" t="n">
         <v>-1.119503264268766</v>
@@ -7222,7 +7048,7 @@
         <v>48</v>
       </c>
       <c r="K52" t="n">
-        <v>0.0002893132626016</v>
+        <v>0.0003106594293751</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
@@ -7270,7 +7096,7 @@
         <v>84</v>
       </c>
       <c r="K53" t="n">
-        <v>0.0004242760525374</v>
+        <v>0.000415474421097</v>
       </c>
       <c r="L53" t="n">
         <v>-0.5127810681254248</v>
@@ -7317,7 +7143,7 @@
         <v>0.014633853595199</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.6760896204391904</v>
+        <v>-0.6612071946411596</v>
       </c>
       <c r="I54" t="n">
         <v>-1.656290751490781</v>
@@ -7326,7 +7152,7 @@
         <v>25</v>
       </c>
       <c r="K54" t="n">
-        <v>0.0151545152436302</v>
+        <v>0.0186255521156091</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
@@ -7365,7 +7191,7 @@
         <v>1.423837909157148e-06</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.6564472035679869</v>
+        <v>-0.6676983149950186</v>
       </c>
       <c r="I55" t="n">
         <v>-1.884925597357834</v>
@@ -7374,7 +7200,7 @@
         <v>84</v>
       </c>
       <c r="K55" t="n">
-        <v>8.935230196762997e-06</v>
+        <v>5.256873326458903e-06</v>
       </c>
       <c r="L55" t="n">
         <v>-0.3574981284246008</v>
@@ -7430,7 +7256,7 @@
         <v>41</v>
       </c>
       <c r="K56" t="n">
-        <v>3.664287061238431e-07</v>
+        <v>3.613992338738726e-07</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
@@ -7469,16 +7295,16 @@
         <v>7.587041157338357e-09</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.4815535453525417</v>
+        <v>-0.4435468996285889</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.710271883078475</v>
+        <v>-1.687580342449948</v>
       </c>
       <c r="J57" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K57" t="n">
-        <v>0.0022441094393604</v>
+        <v>0.0059172754526367</v>
       </c>
       <c r="L57" t="n">
         <v>-0.6112018279066274</v>
@@ -7534,7 +7360,7 @@
         <v>84</v>
       </c>
       <c r="K58" t="n">
-        <v>1.223823803790343e-14</v>
+        <v>1.230602467069931e-14</v>
       </c>
       <c r="L58" t="n">
         <v>-0.4399737585515636</v>
@@ -7581,7 +7407,7 @@
         <v>9.717185228407162e-26</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.6088547188610236</v>
+        <v>-0.609774122900838</v>
       </c>
       <c r="I59" t="n">
         <v>-1.17965095766039</v>
@@ -7590,7 +7416,7 @@
         <v>84</v>
       </c>
       <c r="K59" t="n">
-        <v>1.682892583175507e-23</v>
+        <v>3.049914979167753e-23</v>
       </c>
       <c r="L59" t="n">
         <v>-0.7628762413389161</v>
@@ -7637,16 +7463,16 @@
         <v>2.577727104826952e-08</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.4090209113471007</v>
+        <v>-0.4553564992755945</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.9380407492129508</v>
+        <v>-0.9840077470216833</v>
       </c>
       <c r="J60" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K60" t="n">
-        <v>0.0386019871096417</v>
+        <v>0.0367731878910947</v>
       </c>
       <c r="L60" t="n">
         <v>-0.4812993642776172</v>
@@ -7693,7 +7519,7 @@
         <v>1.862462787286511e-07</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.6029963754797887</v>
+        <v>-0.6066716129543169</v>
       </c>
       <c r="I61" t="n">
         <v>-1.487308219168991</v>
@@ -7702,7 +7528,7 @@
         <v>41</v>
       </c>
       <c r="K61" t="n">
-        <v>3.045796339921663e-06</v>
+        <v>3.199355620446112e-06</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
@@ -7750,7 +7576,7 @@
         <v>34</v>
       </c>
       <c r="K62" t="n">
-        <v>0.07934033189075269</v>
+        <v>0.0806891731745137</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -7789,7 +7615,7 @@
         <v>0.0002745834201577</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.5577920735226907</v>
+        <v>-0.5418257401540657</v>
       </c>
       <c r="I63" t="n">
         <v>-1.294789951947827</v>
@@ -7798,7 +7624,7 @@
         <v>41</v>
       </c>
       <c r="K63" t="n">
-        <v>0.0064239948066587</v>
+        <v>0.0075179236778412</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
@@ -7837,7 +7663,7 @@
         <v>0.0279722451553964</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.5718840793004215</v>
+        <v>-0.5725285141593792</v>
       </c>
       <c r="I64" t="n">
         <v>-1.116740050192469</v>
@@ -7846,7 +7672,7 @@
         <v>20</v>
       </c>
       <c r="K64" t="n">
-        <v>0.0883505594342287</v>
+        <v>0.0927050260202586</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
@@ -7885,16 +7711,16 @@
         <v>4.258551822811394e-05</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.5636654021093819</v>
+        <v>-0.5147951748550157</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.396319646891632</v>
+        <v>-1.346559113584217</v>
       </c>
       <c r="J65" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K65" t="n">
-        <v>3.321251395947969e-05</v>
+        <v>0.0001556977199323</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
@@ -7933,16 +7759,16 @@
         <v>0.0219996384546613</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.2488876797106725</v>
+        <v>-0.3196041051201983</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.287752262301766</v>
+        <v>-1.34613456465733</v>
       </c>
       <c r="J66" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K66" t="n">
-        <v>0.2785379727352818</v>
+        <v>0.2533678553426165</v>
       </c>
       <c r="L66" t="n">
         <v>-0.2911837936060775</v>
@@ -7989,7 +7815,7 @@
         <v>1.349682588543661e-15</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.5565204289985366</v>
+        <v>-0.555194939516346</v>
       </c>
       <c r="I67" t="n">
         <v>-1.063319948759066</v>
@@ -7998,7 +7824,7 @@
         <v>84</v>
       </c>
       <c r="K67" t="n">
-        <v>3.549690913961492e-15</v>
+        <v>2.729560956091672e-15</v>
       </c>
       <c r="L67" t="n">
         <v>-0.6279951107005773</v>
@@ -8045,16 +7871,16 @@
         <v>4.284868007069782e-10</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.5004788604295689</v>
+        <v>-0.4995383926737027</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.474191718246479</v>
+        <v>-1.479739523725293</v>
       </c>
       <c r="J68" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K68" t="n">
-        <v>0.0024683274903745</v>
+        <v>0.005048902141721</v>
       </c>
       <c r="L68" t="n">
         <v>-0.3568471092676095</v>
@@ -8069,7 +7895,7 @@
         <v>4.175254393929171e-05</v>
       </c>
       <c r="P68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -8101,7 +7927,7 @@
         <v>4.094093783348658e-09</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.5990627487169113</v>
+        <v>-0.6085127516491038</v>
       </c>
       <c r="I69" t="n">
         <v>-1.001921012931471</v>
@@ -8110,7 +7936,7 @@
         <v>41</v>
       </c>
       <c r="K69" t="n">
-        <v>4.594529102577612e-08</v>
+        <v>3.924242660003469e-08</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
@@ -8149,7 +7975,7 @@
         <v>6.576459422400148e-09</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.5323682255846232</v>
+        <v>-0.5265208469433831</v>
       </c>
       <c r="I70" t="n">
         <v>-1.302407584499616</v>
@@ -8158,7 +7984,7 @@
         <v>41</v>
       </c>
       <c r="K70" t="n">
-        <v>4.296737805193369e-08</v>
+        <v>5.083877287422035e-08</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
@@ -8197,7 +8023,7 @@
         <v>0.0003689996347558</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.5926420905757489</v>
+        <v>-0.5862287197015303</v>
       </c>
       <c r="I71" t="n">
         <v>-1.566429850753121</v>
@@ -8206,7 +8032,7 @@
         <v>31</v>
       </c>
       <c r="K71" t="n">
-        <v>0.0004842721442039</v>
+        <v>0.0006659715776589</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
@@ -8245,7 +8071,7 @@
         <v>6.367010255776581e-05</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.498996148327588</v>
+        <v>-0.4917411209538229</v>
       </c>
       <c r="I72" t="n">
         <v>-1.728922644651206</v>
@@ -8254,7 +8080,7 @@
         <v>48</v>
       </c>
       <c r="K72" t="n">
-        <v>0.0001693464355643</v>
+        <v>0.0002194727846313</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
@@ -8293,16 +8119,16 @@
         <v>0.009851936652814501</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.6062360270292859</v>
+        <v>-0.6237683391940227</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.632766486566417</v>
+        <v>-1.649456557637444</v>
       </c>
       <c r="J73" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K73" t="n">
-        <v>0.1599896037585612</v>
+        <v>0.1683544540301084</v>
       </c>
       <c r="L73" t="n">
         <v>-0.3038429749596735</v>
@@ -8358,7 +8184,7 @@
         <v>41</v>
       </c>
       <c r="K74" t="n">
-        <v>1.686895039140194e-06</v>
+        <v>1.779390686367688e-06</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
@@ -8397,16 +8223,16 @@
         <v>0.0001486493977577</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.4352483666126812</v>
+        <v>-0.4885444924735607</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.194382311439327</v>
+        <v>-1.238547504582328</v>
       </c>
       <c r="J75" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K75" t="n">
-        <v>0.2104465416348919</v>
+        <v>0.1343938131725688</v>
       </c>
       <c r="L75" t="n">
         <v>-0.6210210124911151</v>
@@ -8453,7 +8279,7 @@
         <v>0.0009944628036820001</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.5423622730601331</v>
+        <v>-0.5452268213664281</v>
       </c>
       <c r="I76" t="n">
         <v>-1.540676236530749</v>
@@ -8462,7 +8288,7 @@
         <v>41</v>
       </c>
       <c r="K76" t="n">
-        <v>0.0041284586733647</v>
+        <v>0.0036932878203681</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
@@ -8510,7 +8336,7 @@
         <v>41</v>
       </c>
       <c r="K77" t="n">
-        <v>0.034174674235439</v>
+        <v>0.0342254628041966</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
@@ -8549,7 +8375,7 @@
         <v>3.321059925924584e-07</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.5514324040065232</v>
+        <v>-0.5572949443334795</v>
       </c>
       <c r="I78" t="n">
         <v>-1.228344299228768</v>
@@ -8558,7 +8384,7 @@
         <v>41</v>
       </c>
       <c r="K78" t="n">
-        <v>1.975659368840335e-06</v>
+        <v>1.830180729489149e-06</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
@@ -8597,7 +8423,7 @@
         <v>9.844976616303546e-16</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.554971609039457</v>
+        <v>-0.5603182364109947</v>
       </c>
       <c r="I79" t="n">
         <v>-1.273802327287748</v>
@@ -8606,7 +8432,7 @@
         <v>84</v>
       </c>
       <c r="K79" t="n">
-        <v>7.909782411107524e-15</v>
+        <v>5.811419108649426e-15</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
@@ -8645,7 +8471,7 @@
         <v>6.193757781546877e-05</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.5440469271664343</v>
+        <v>-0.5428871644383437</v>
       </c>
       <c r="I80" t="n">
         <v>-1.252704173171887</v>
@@ -8654,7 +8480,7 @@
         <v>18</v>
       </c>
       <c r="K80" t="n">
-        <v>0.0001159661143548</v>
+        <v>0.000120241792565</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
@@ -8693,7 +8519,7 @@
         <v>1.534968605201089e-06</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.5569823962311936</v>
+        <v>-0.5590509717882922</v>
       </c>
       <c r="I81" t="n">
         <v>-1.005616970228762</v>
@@ -8702,7 +8528,7 @@
         <v>41</v>
       </c>
       <c r="K81" t="n">
-        <v>1.566136615861523e-06</v>
+        <v>1.212063833928408e-06</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
@@ -8741,7 +8567,7 @@
         <v>0.0038629789199848</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.5671855278829783</v>
+        <v>-0.5650579904840343</v>
       </c>
       <c r="I82" t="n">
         <v>-2.004145108267159</v>
@@ -8750,7 +8576,7 @@
         <v>18</v>
       </c>
       <c r="K82" t="n">
-        <v>0.0020106892733261</v>
+        <v>0.0021642652918387</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
@@ -8789,16 +8615,16 @@
         <v>0.0001009451508118</v>
       </c>
       <c r="H83" t="n">
-        <v>-0.5121968458560141</v>
+        <v>-0.5298575917415111</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.050899938523135</v>
+        <v>-1.067771506055804</v>
       </c>
       <c r="J83" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K83" t="n">
-        <v>0.0091482550802856</v>
+        <v>0.0071672730295836</v>
       </c>
       <c r="L83" t="n">
         <v>-0.2036825766095725</v>
@@ -8845,16 +8671,16 @@
         <v>0.0249337276191208</v>
       </c>
       <c r="H84" t="n">
-        <v>-0.4667918258867726</v>
+        <v>-0.4362957343224759</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.427061562324617</v>
+        <v>-1.406445794546605</v>
       </c>
       <c r="J84" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K84" t="n">
-        <v>0.3035427378777632</v>
+        <v>0.5265313329147079</v>
       </c>
       <c r="L84" t="n">
         <v>-0.3832017821509078</v>
@@ -8901,7 +8727,7 @@
         <v>4.987669942023617e-10</v>
       </c>
       <c r="H85" t="n">
-        <v>-0.5240646762003673</v>
+        <v>-0.5205004817451246</v>
       </c>
       <c r="I85" t="n">
         <v>-1.69167040036456</v>
@@ -8910,7 +8736,7 @@
         <v>41</v>
       </c>
       <c r="K85" t="n">
-        <v>2.427966385586572e-10</v>
+        <v>2.690770804960845e-10</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
@@ -8949,7 +8775,7 @@
         <v>0.0044973468121676</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.5167185017318694</v>
+        <v>-0.5130590587252496</v>
       </c>
       <c r="I86" t="n">
         <v>-1.054139446371316</v>
@@ -8958,7 +8784,7 @@
         <v>25</v>
       </c>
       <c r="K86" t="n">
-        <v>0.0111053552608081</v>
+        <v>0.0122965115969223</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
@@ -8997,16 +8823,16 @@
         <v>4.29766077872804e-05</v>
       </c>
       <c r="H87" t="n">
-        <v>-0.4311470999093539</v>
+        <v>-0.4632235940676168</v>
       </c>
       <c r="I87" t="n">
-        <v>-1.001603889731879</v>
+        <v>-1.035102832407292</v>
       </c>
       <c r="J87" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K87" t="n">
-        <v>0.0795483180009368</v>
+        <v>0.0604288075955792</v>
       </c>
       <c r="L87" t="n">
         <v>-0.5802961783019381</v>
@@ -9053,7 +8879,7 @@
         <v>0.0275583139153067</v>
       </c>
       <c r="H88" t="n">
-        <v>-0.4964774484474189</v>
+        <v>-0.4978560908971277</v>
       </c>
       <c r="I88" t="n">
         <v>-1.131728656938623</v>
@@ -9062,7 +8888,7 @@
         <v>18</v>
       </c>
       <c r="K88" t="n">
-        <v>0.0750701660062968</v>
+        <v>0.0774111209668804</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
@@ -9101,7 +8927,7 @@
         <v>5.340247565739578e-09</v>
       </c>
       <c r="H89" t="n">
-        <v>-0.4877125905899441</v>
+        <v>-0.4871893024619198</v>
       </c>
       <c r="I89" t="n">
         <v>-0.982198430131472</v>
@@ -9110,7 +8936,7 @@
         <v>84</v>
       </c>
       <c r="K89" t="n">
-        <v>2.484655038981622e-06</v>
+        <v>3.290544513526346e-06</v>
       </c>
       <c r="L89" t="n">
         <v>-0.6064159015923158</v>
@@ -9157,7 +8983,7 @@
         <v>1.06422308206578e-19</v>
       </c>
       <c r="H90" t="n">
-        <v>-0.5127867146427008</v>
+        <v>-0.5089987898773374</v>
       </c>
       <c r="I90" t="n">
         <v>-1.667128592661345</v>
@@ -9166,7 +8992,7 @@
         <v>84</v>
       </c>
       <c r="K90" t="n">
-        <v>3.824575990023873e-19</v>
+        <v>4.491567743166637e-19</v>
       </c>
       <c r="L90" t="n">
         <v>-0.3081806729241598</v>
@@ -9213,7 +9039,7 @@
         <v>5.964359992334674e-05</v>
       </c>
       <c r="H91" t="n">
-        <v>-0.5275284761511621</v>
+        <v>-0.521998747401327</v>
       </c>
       <c r="I91" t="n">
         <v>-1.059438818055799</v>
@@ -9222,7 +9048,7 @@
         <v>41</v>
       </c>
       <c r="K91" t="n">
-        <v>2.755419649859143e-05</v>
+        <v>2.579919583240058e-05</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
@@ -9261,16 +9087,16 @@
         <v>6.045980679281802e-07</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.3483339154991181</v>
+        <v>-0.343636194633617</v>
       </c>
       <c r="I92" t="n">
-        <v>-1.004022096497996</v>
+        <v>-0.9993243756324952</v>
       </c>
       <c r="J92" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K92" t="n">
-        <v>0.0031236034966397</v>
+        <v>0.0124244570045844</v>
       </c>
       <c r="L92" t="n">
         <v>-0.7069494138384081</v>
@@ -9317,16 +9143,16 @@
         <v>0.0004240070090427</v>
       </c>
       <c r="H93" t="n">
-        <v>-0.4876295122398688</v>
+        <v>-0.4851362243536568</v>
       </c>
       <c r="I93" t="n">
         <v>-2.54965578196946</v>
       </c>
       <c r="J93" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K93" t="n">
-        <v>0.0343736861157788</v>
+        <v>0.0407274094688463</v>
       </c>
       <c r="L93" t="n">
         <v>-0.2078791465553813</v>
@@ -9382,7 +9208,7 @@
         <v>10</v>
       </c>
       <c r="K94" t="n">
-        <v>0.08330944031554451</v>
+        <v>0.0841953498140964</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
@@ -9427,10 +9253,10 @@
         <v>-1.459587683391078</v>
       </c>
       <c r="J95" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K95" t="n">
-        <v>0.1613215366834358</v>
+        <v>0.2343814062292564</v>
       </c>
       <c r="L95" t="n">
         <v>-0.1932652040340934</v>

--- a/figures/supporting_information/S7_Table.xlsx
+++ b/figures/supporting_information/S7_Table.xlsx
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Discovery cohort: the 878 DepMap 26Q1 cancer cell lines without any Sanger (KY-library) screen in the combined 26Q1 data set; the complete procedure (one-sided Mann-Whitney, BH over all tests, q &lt; 0.05, median Chronos &lt; -1, selectivity &lt; -0.5) was applied to it.</t>
+          <t>Discovery cohort: the 856 DepMap 26Q1 cancer cell lines without any Sanger (KY-library) screen in the combined 26Q1 data set, after excluding 22 models derived from the same patient as a Project Score model; the complete procedure (one-sided Mann-Whitney, BH over all tests, q &lt; 0.05, median Chronos &lt; -1, selectivity &lt; -0.5) was applied to it.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Replication: the same procedure applied to the Sanger Project Score Chronos data (316 cancer models); discovery and replication share no screens and no cell lines.</t>
+          <t>Replication: the same procedure applied to the Sanger Project Score Chronos data (316 cancer models); discovery and replication share no screens, models or patients.</t>
         </is>
       </c>
     </row>
@@ -462,7 +462,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sheet 'Overlapping comparison (not independent)': earlier comparison of the primary candidates with the Sanger data. For the shared cell lines the 26Q1 gene effects include the same Sanger screens, so this comparison is not independent; shown for transparency only.</t>
+          <t>Sheet 'Overlapping (not independent)': earlier comparison of the primary candidates with the Sanger data. For the shared cell lines the 26Q1 gene effects include the same Sanger screens, so this comparison is not independent; shown for transparency only.</t>
         </is>
       </c>
     </row>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>confidence</t>
+          <t>Low-n flag (fewer than 10 target lines)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
